--- a/outbreaks/results/dxri_20250212.xlsx
+++ b/outbreaks/results/dxri_20250212.xlsx
@@ -623,7 +623,7 @@
         <v>28</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -679,7 +679,7 @@
         <v>111</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1235,7 +1235,7 @@
         <v>28</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1291,7 +1291,7 @@
         <v>111</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1847,7 @@
         <v>10.48689138576779</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1903,7 +1903,7 @@
         <v>41.57303370786517</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -2485,10 +2485,10 @@
         <v>10.48689138576779</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>7.643743080440195</v>
+        <v>21.92945736615448</v>
       </c>
     </row>
     <row r="10">
@@ -2547,10 +2547,10 @@
         <v>41.57303370786517</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>26.82462541293178</v>
+        <v>41.11033969864606</v>
       </c>
     </row>
     <row r="12">
